--- a/AAII_Financials/Quarterly/SCCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>SCCO</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4289000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4251400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3869800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3377300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3051000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3121900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2784400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2930900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3118300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2599800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2295600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2505600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2300700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2793900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2820300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2156900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2306900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2763800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2823700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2680900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2897000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2532500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2350700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2129100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1785400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1719700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1854600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1859500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1818000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1753400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1694600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1723700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1837200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1841100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1864300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1676500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1529800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1583900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1399000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1400700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1389500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1469400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1442400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1356800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1211700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1290400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1183200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1223100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1252900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1129100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1141600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1175700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1147700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1165100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1177800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1109000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1217900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1028900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1015300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>898900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>956900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>915200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1011800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>911600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>937600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>926900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>960900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>877300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>838500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>815300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>856800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>824000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>851700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>876500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>822600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>781500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>804800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>843800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>724200</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>831400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2899500</v>
+      </c>
+      <c r="E10" s="3">
         <v>2782000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2427400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2020500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1839300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1831500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1601200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1707800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1865400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1470700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1154000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1329900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1153000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1628800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1642500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1047900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1089000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1734900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1808400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1782000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1940100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1617300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1338900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1217500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>847800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>792800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>893700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>982200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>979500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>938100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>837800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>899700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>985500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>964600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1041700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>895000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>725000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>740100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>674800</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>569300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1279,86 +1293,89 @@
       <c r="P12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" s="3">
         <v>11100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>11700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>16600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>6900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>5500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>9900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>8100</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>5700</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>5100</v>
-      </c>
-      <c r="AO12" s="3">
-        <v>9700</v>
       </c>
       <c r="AP12" s="3">
         <v>9700</v>
       </c>
+      <c r="AQ12" s="3">
+        <v>9700</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,43 +1496,46 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3">
         <v>-9900</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3">
         <v>9900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-16200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-15000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>24</v>
@@ -1523,14 +1543,14 @@
       <c r="P14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>24</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>24</v>
@@ -1547,17 +1567,17 @@
       <c r="X14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z14" s="3">
         <v>8700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>10500</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>24</v>
@@ -1571,8 +1591,8 @@
       <c r="AF14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>226000</v>
+      </c>
+      <c r="E15" s="3">
         <v>225700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>230700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>207800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>206200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>223800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>214200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>213100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>209600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>209000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>208200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>212500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>209200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>203700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>198700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>192000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>209000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>196600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>206600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>203400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>195400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>200600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>192800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>196000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>193800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>192900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>183800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>200300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>198800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>181600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>179100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>170600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>162600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>162000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>177300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>169300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>171200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>153400</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>172800</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1665700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1771100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1759300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1608500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1464100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1586400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1477000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1480600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1515000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1410100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1426900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1436400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1400000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1440200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1450200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1369700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1498400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1293700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1293200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1173100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1221800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1180900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1284300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1185200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1208200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1186400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1222800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1145700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1104400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1059700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1071100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1027000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1049600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1067800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1034300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>983900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1003900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1013500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>928500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1038300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2623300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2480300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2110500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1768800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1586900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1535500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1307400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1450300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1603300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1189700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>868700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1069200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>900700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1353700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1370100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>787200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>808500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1470100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1530500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1507800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1675200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1351600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1066400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>943900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>577200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>533300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>631800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>713800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>713600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>693700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>623500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>696700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>787600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>773300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>830000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>692600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>525900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>570400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>470500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>362400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-35600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>25100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-900</v>
-      </c>
       <c r="H20" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>32800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>13300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>81000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>46500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>16300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-20900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>27400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>9100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-15800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>4400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>5700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-38400</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2876400</v>
+      </c>
+      <c r="E21" s="3">
         <v>2741600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2316100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1981800</v>
       </c>
-      <c r="G21" s="3">
-        <v>1794000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1799700</v>
+      </c>
+      <c r="I21" s="3">
         <v>1758800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1488800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1669100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1803000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1424400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1063600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1290500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1111700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1561500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1649800</v>
-      </c>
-      <c r="R21" s="3">
-        <v>1025700</v>
       </c>
       <c r="S21" s="3">
         <v>1025700</v>
       </c>
       <c r="T21" s="3">
+        <v>1025700</v>
+      </c>
+      <c r="U21" s="3">
         <v>1683000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1728500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1710800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1863700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1556900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1258400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1128700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>774400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>726600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>794700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>912800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>939800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>884400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>791200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>864100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>949900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>935600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>991500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>857400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>701500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>729500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>604900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>548300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E22" s="3">
         <v>89800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>92000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>91300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>94000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>91900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>87300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>83300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>80500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>80900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>81500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>81600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>82700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>82900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>84200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>85200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>87700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>89300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>88900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>89300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>89600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>88700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>89200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>92100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>96800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>95100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>83800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>84000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>77800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>70100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>69200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>68600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>69200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>70600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>71600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>73000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>90800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>70600</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>73100</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2619900</v>
+      </c>
+      <c r="E23" s="3">
         <v>2472900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2053300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1730600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1552600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1481900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1242800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1426200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1532600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1162200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>795900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1017300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>844100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1296400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1368200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>749500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>731500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1398700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1432600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1418500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1579000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1266700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>976900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>843500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>488400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>436900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>515800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>628800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>657000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>625000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>542000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>624300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>718700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>704400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>743600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>616600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>457300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>485300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>361500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>300700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>945300</v>
+      </c>
+      <c r="E24" s="3">
         <v>891000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>741800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>619700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>576000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>532800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>446600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>526400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>578800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>423400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>348700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>395300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>294500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>480500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>459100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>228500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>296400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>612100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>595400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>548600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>647700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>507500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>389700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>338500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>224400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>221700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>215300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>241000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>251100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>237900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>219000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>257900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>309100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>236600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>250900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>220100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>160300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>176200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>195700</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>111200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1674600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1581900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1311500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1110900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>976600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>949100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>796200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>899800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>953800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>738800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>447200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>622000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>549600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>815900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>909100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>521000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>435100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>786600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>837200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>869900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>931300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>759200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>587200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>505000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>264000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>215200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>300500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>387800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>405900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>387100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>323000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>366400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>409600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>467800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>492700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>396500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>297000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>309100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>165800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>189500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1576900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1307900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1107600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>973400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>945900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>793900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>896700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>950200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>736000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>445000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>619500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>547500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>813200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>902400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>519000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>432300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>784700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>832900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>867600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>932700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>763800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>590100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>506000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>259500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>214800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>305600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>389600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>402400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>388200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>324100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>369400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>409600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>470700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>498400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>401800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>299700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>314400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>171900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>197600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3224,8 +3285,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -3242,11 +3303,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-30900</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-785900</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E32" s="3">
         <v>35600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-25100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5200</v>
       </c>
-      <c r="G32" s="3">
-        <v>900</v>
-      </c>
       <c r="H32" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-32800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-13300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-81000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-46500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-16300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>11200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>20900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-27400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-9100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>11400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>15800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>4400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>38400</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1576900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1307900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1107600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>973400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>945900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>793900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>896700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>950200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>736000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>445000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>619500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>547500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>813200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>902400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>519000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>432300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>784700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>832900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>867600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>932700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>763800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>590100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>506000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>259500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>214800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>305600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>389600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>402400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>388200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>293200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>369400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>409600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>470700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-287500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>401800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>299700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>314400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>171900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>197600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1576900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1307900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1107600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>973400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>945900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>793900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>896700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>950200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>736000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>445000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>619500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>547500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>813200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>902400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>519000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>432300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>784700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>832900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>867600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>932700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>763800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>590100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>506000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>259500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>214800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>305600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>389600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>402400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>388200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>293200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>369400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>409600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>470700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-287500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>401800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>299700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>314400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>171900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>197600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,1106 +4305,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5665000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4915400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4304600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3949600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3334900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4116300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3258100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2654800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1875300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1252200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1151500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1967100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2199000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2299800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2069700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2184500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2113100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2847200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3002000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2583700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2394300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2267300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2183600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2145400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1808800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2051600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1925100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1935200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>752200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>737000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>844600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>967300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1032500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1068200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1004800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>798500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>688700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>698700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>546000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>511500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1664900</v>
+      </c>
+      <c r="E42" s="3">
         <v>434100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>604600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>575900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>675400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>218200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>245300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>318800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>329100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>329300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>599300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>247100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>140600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>208300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>242600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>406500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>486900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>626800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>545800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>415900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>410800</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>30700</v>
       </c>
       <c r="AA42" s="3">
         <v>30700</v>
       </c>
       <c r="AB42" s="3">
+        <v>30700</v>
+      </c>
+      <c r="AC42" s="3">
         <v>40700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>80700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>118800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>213500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>213800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>236500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>50700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>56500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>50500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>30500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>40200</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>52700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>51300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>100800</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2074700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2079700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2022600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1790400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1627800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1605100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1243800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1589400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1704000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1395000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1228300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1211100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1157300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1326700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1473800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1154700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1146400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1255200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1446600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1579800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1506600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1324400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1136600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1036800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>937700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>789700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>911800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>918600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>935700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1035400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>972600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>943000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>963300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1009700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>976400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>976800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>743100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>769800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>668500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>664300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1060900</v>
+      </c>
+      <c r="E44" s="3">
         <v>959200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1058100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1031300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1005200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>966100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1048900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>990500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1017200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1014400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1016900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>975500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>985300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>981800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1013900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1053300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1071600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1029900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>972900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>912500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>893900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>880700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>950200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>977300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>980400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1079400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1068500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1062200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1068600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1035600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1032700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1007600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1003500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1049800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1041900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>997400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>975400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>979900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1010400</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>972600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E45" s="3">
         <v>32600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>31400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>24800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>23200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>39300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>41500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>55900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>422000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>566500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>395100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>229700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>231200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>188000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>170900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>148000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>134000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>147600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>102100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>178300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>198600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>259900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>222800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>160900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>116300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>118800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>119500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>133000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>96500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>149200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>197300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>272700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>289900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>300600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10787500</v>
+      </c>
+      <c r="E46" s="3">
         <v>8717000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8352500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7669600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7002400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7220000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6174300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5926400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5333700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4440800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4429500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4748000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4769600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5197700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5187700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4959300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4968800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5768500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6139600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5890800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5511500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5036300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4815200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4337800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3859700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4139700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4184700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4177600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3098100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3182400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3180000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3273200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3169500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3317200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3170100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2952400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2644700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2773800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2566100</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2549800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>160900</v>
+      </c>
+      <c r="E47" s="3">
         <v>150700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>134500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>123600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>120800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>115000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>111900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>114000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>114500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>113900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>108200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>100100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>100200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>103900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>110800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>115700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>115800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>116700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>115400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>120500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>123400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>118200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>114300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>168000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>165400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>171900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>171400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>167900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>103000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>104700</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>103600</v>
       </c>
       <c r="AH47" s="3">
         <v>103600</v>
       </c>
       <c r="AI47" s="3">
+        <v>103600</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>100200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>100000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>99700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>95800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>91500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>90200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>87500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>83700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11316200</v>
+      </c>
+      <c r="E48" s="3">
         <v>11142100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10973000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10685500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10615700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10655300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10622800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10652100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10616900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10540300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10558300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10517700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10501700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10446500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10448000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10424200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10405500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10393700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10380700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10402700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10400400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10416300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10437700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10139400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10208200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10318300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10417400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10457000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10490900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>10476100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9403800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9311800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9172600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9118500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>9099600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>8928300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>8837500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>8755900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>8766500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>8581400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>121500</v>
+      </c>
+      <c r="E49" s="3">
         <v>122600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>122400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>120900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>121700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>122600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>124600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>125400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>127300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>128800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>130200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>130500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>132400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>134500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>134700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>137200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>135100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>136800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>138100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>139000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>140100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>141500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>143000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>144800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>145900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>148500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>148400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>152000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>148200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>147300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>147700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>150800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>151800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>153100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>152500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>147000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>146800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>155500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>154200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>152900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1404500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1445000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1462700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1457600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1433700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1389600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1369300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1323700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1316300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1312300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1243000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1211700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1199900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1179500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1396200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1446800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1496300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1483200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1523800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1557300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1520000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1505500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1436300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1458400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1425800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1433700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1485500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1539900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1504400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1632100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1452500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1477300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1451800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1349300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1258200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1858900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1794800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1747600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1660000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1695200</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24127700</v>
+      </c>
+      <c r="E54" s="3">
         <v>21929900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21381400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20331800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19554700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19791200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18713500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18415500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17777700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16789300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16725300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16965000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16939500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17323300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17277400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17083200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17121500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17898900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18297600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18110300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17695400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17217800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16946500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16248400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15805000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16212100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>16407400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16494400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15344600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15542600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14287600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14316700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>14045900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>14038100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>13780100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>13982400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>13515300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>13523000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>13234300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>13063000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,189 +6145,193 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>871900</v>
+      </c>
+      <c r="E57" s="3">
         <v>906000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>861500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>739200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>647200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>684400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>615200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>608800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>647200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>748500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>652600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>618500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>610100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>662600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>537400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>501500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>529400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>579400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>488600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>498500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>470900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>441900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>490300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>467200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>429100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>516200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>598300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>497500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>564100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>520900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1271500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>609000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>562200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>581100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>569700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>482000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>449700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>428200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>522000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>479400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>95600</v>
+      </c>
+      <c r="E58" s="3">
         <v>88500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>86500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>85400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>84000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>583100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>581600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>575300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>576400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>77000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>78000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>71800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>74900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>76200</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>300000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>299900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>299800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>299700</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>24</v>
@@ -6205,35 +6339,35 @@
       <c r="X58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3" t="s">
+      <c r="Y58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>400000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>399800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>399700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>399600</v>
       </c>
-      <c r="AF58" s="3" t="s">
+      <c r="AG58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH58" s="3" t="s">
-        <v>24</v>
+      <c r="AH58" s="3">
+        <v>0</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>24</v>
@@ -6241,8 +6375,8 @@
       <c r="AJ58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK58" s="3">
-        <v>0</v>
+      <c r="AK58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AL58" s="3">
         <v>0</v>
@@ -6259,496 +6393,511 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>704800</v>
+      </c>
+      <c r="E59" s="3">
         <v>460400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>634500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>398200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>264600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>260100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>635300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>531800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>364800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>142300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>278300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>213600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>85000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>100800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>698300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>683300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>679100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>846600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1461700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1290600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>981200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>933000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>894500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>694500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>462700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>471000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>478400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>535000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>421700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>602500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>618200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>598900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>444000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>598700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>598600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>497800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>351100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>561300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>477000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>455700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2132000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1992400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2145100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1698000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1329000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1944400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2248100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2139400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1898200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1340000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1388500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1284100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1060600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1247300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1235700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1484800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1508400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1725800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2250000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1789100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1452100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1374900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1384800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1161700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>891800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1387200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1476500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1432200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1385400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1123400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1216300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1207900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1006200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1179800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1168300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>979800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>800800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>989500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>999000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>935100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8528800</v>
+      </c>
+      <c r="E61" s="3">
         <v>7313200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7327000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7347400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7364900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7384600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6416100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6407100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6425500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6935600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6952000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6968900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6991600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7008500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6251200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6250300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6249500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6248700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6247900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6546700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6545900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6545000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6544200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6543400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6542600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6541800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6541000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6540400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5562100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5960900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5960100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5959300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5958500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5957800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5957100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5956300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5955600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5954900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5954200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5953500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>643800</v>
+      </c>
+      <c r="E62" s="3">
         <v>654500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>673900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>638100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>671000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>694700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>686600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>746100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>735000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>757900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>771400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>758800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>733600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>707400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1643600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1720100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1676600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1703800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1591900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1621100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1724600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1719600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1741500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1474100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1501000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1519900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1531700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1651500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1608500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1765500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>498400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>519000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>512100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>511100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>505300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>416200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>426700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>454600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>410200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11419100</v>
+      </c>
+      <c r="E66" s="3">
         <v>10070500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10276500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9814900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9501300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10154500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9475300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9426100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9217500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9183400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9244100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9156800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8976900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9134900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9193200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9516400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9494300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9738200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10148400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10014300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9777900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9692700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9721700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9229200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8983500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9495900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9597100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9673100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8604300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8896100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7720200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7730600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7520200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7691300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7672400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7392900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7223000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7438300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7402000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7366700</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4588100</v>
+      </c>
+      <c r="E72" s="3">
         <v>5292700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5797200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6116000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6459400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6682800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6839600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7142800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7180900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7156700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7033500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7361500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7516800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7742400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7702300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7186500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7247300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7781300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7769700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7709800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7538000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7146400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6846400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6642800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6446100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6341200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6435600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6439200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6358700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6265700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6186900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6203000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6142800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5965000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5726200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6211300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5914300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5707500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>5455300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>5316100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12632200</v>
+      </c>
+      <c r="E76" s="3">
         <v>11787600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11038100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10449900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9984800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9568300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9171600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8921000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8492500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7541700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7418100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7744800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7899600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8124800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8084200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7566800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7627200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8160700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8149200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8096000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7917500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7525100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7224800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7019200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6821500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6716200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6810300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6821300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6740300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6646500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6567400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6586100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6525700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6346800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6107700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6589500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6292300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6084700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5832300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5696300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1670000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1576900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1307900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1107600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>973400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>945900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>793900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>896700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>950200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>736000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>445000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>619500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>547500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>813200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>902400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>519000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>432300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>784700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>832900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>867600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>932700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>763800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>590100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>506000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>259500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>214800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>305600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>389600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>402400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>388200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>293200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>369400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>409600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>470700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-287500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>401800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>299700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>314400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>171900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>197600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>206200</v>
+      </c>
+      <c r="E83" s="3">
         <v>223800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>205100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>213100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>209600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>209000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>212500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>209200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>203700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>191400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>192000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>209000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>196600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>198700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>192000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>209000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>196600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>206600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>203400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>195400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>200600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>192800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>196000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>193900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>192900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>183800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>200200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>198800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>181600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>179100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>170600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>162600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>162000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>177300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>169200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>171200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>153400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>172800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>174500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1988500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1694500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1494300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1559600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>976800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>721400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1360500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1439400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>962100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>659700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>541000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1049800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>797100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1185200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1081900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>590000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>309900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>820700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1227600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1220600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1061600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>782600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1095600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>793500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>419400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>475100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>541400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>585200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>414000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>371300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>446200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>732800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>406300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>649800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>696600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>436100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>353800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>490100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>287200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>307100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-422800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-441900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-422600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-349200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-235700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-317800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-235300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-246400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-331800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-213800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-255400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-262700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-252500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-238100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-290900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-227900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-224500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-205200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-196800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-243100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-219800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-232600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-243400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-134500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-113300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-101000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-171400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-182600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-180400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-173100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-289600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-282200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-253900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-295700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-313100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-212700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-252100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-245600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-278000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-275600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1653600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-271300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-451300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-249700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-692900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-290700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-161800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-236000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-331700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>56200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-607000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-509000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-112100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-170400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-495800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>14500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-60600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-124900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-60800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-314200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-360100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-237800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-618200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-133700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-103300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-60600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-250100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-65500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-85600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-172800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-266400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-467900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-260500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-301400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-330400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-203200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-238800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-246600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-228000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-202000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,40 +10455,41 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>826200</v>
+      </c>
+      <c r="E96" s="3">
         <v>819200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>731100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>643300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>557400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>553300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>549900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>468800</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>618500</v>
-      </c>
-      <c r="M96" s="3">
-        <v>773100</v>
       </c>
       <c r="N96" s="3">
         <v>773100</v>
@@ -10267,40 +10501,40 @@
         <v>773100</v>
       </c>
       <c r="Q96" s="3">
+        <v>773100</v>
+      </c>
+      <c r="R96" s="3">
         <v>-386500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-579800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-966400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-773100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-773000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-695800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-541200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-463800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-386500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-309300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-154600</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-309200</v>
       </c>
       <c r="AC96" s="3">
         <v>-309200</v>
@@ -10309,43 +10543,46 @@
         <v>-309200</v>
       </c>
       <c r="AE96" s="3">
+        <v>-309200</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-309300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-309200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-309300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-309200</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-231900</v>
       </c>
       <c r="AJ96" s="3">
         <v>-231900</v>
       </c>
       <c r="AK96" s="3">
+        <v>-231900</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-193300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-108200</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-92800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-61800</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-38700</v>
       </c>
       <c r="AP96" s="3">
         <v>-38700</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-38700</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>417500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-819100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-731500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-648200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1060400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>432900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-554000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-471000</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="L100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-620100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-775500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-775100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-775800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-774700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-687700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-580100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-968400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-774800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-775100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-697400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-542600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-465100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-388200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-308900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-554800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-311400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-311500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>667500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-308900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-309300</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>-309400</v>
       </c>
       <c r="AH100" s="3">
         <v>-309400</v>
       </c>
       <c r="AI100" s="3">
+        <v>-309400</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-231800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-232800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-193400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-108400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-92500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-61800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-38700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-41300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>47100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>25900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-10000</v>
       </c>
       <c r="L101" s="3">
         <v>-10000</v>
       </c>
       <c r="M101" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="N101" s="3">
         <v>-13200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>47000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-15000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-75800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-13200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>47000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-15000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-75800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>26600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-19600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-31900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-51000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-14300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>23400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-20700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>50300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-52200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>33500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-14700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-32500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-29000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>14000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>749700</v>
+      </c>
+      <c r="E102" s="3">
         <v>610800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>355100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>614600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-781400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>858200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>603400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>779500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>623100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-815600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-231900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>230100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-114800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>71400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-734100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-154800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>418300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>189400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>127000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>83700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>38200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>336600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-242800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>126500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1183000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>15200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-107600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-122700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-65200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-35700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>63400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>206300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>109800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-10000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>152700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>34500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>59000</v>
       </c>
     </row>
